--- a/MEME_OUTPUT/direct_meme_out_1_motif1.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_1_motif1.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>0.05017992802878848</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.165</v>
+        <v>0.1651339464214314</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9106</v>
+        <v>0.9104358256697321</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8124</v>
+        <v>0.8122750899640144</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.9106</v>
+        <v>0.9104358256697321</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.9704</v>
+        <v>0.9702119152339065</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.9728</v>
+        <v>0.9726109556177529</v>
       </c>
     </row>
     <row r="11">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9872051179528188</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/direct_meme_out_1_motif1.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_1_motif1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>GTCACAAAAGTGTCA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GTCA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GTCA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CAAAAGT&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.05017992802878848</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AAAA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.1651339464214314</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>CACA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9104358256697321</v>
       </c>
     </row>
@@ -564,7 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAGGTCACAA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,7 +612,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGGTCAC&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -593,7 +643,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAGGTCACAAA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,7 +651,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGGTCACA&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -622,7 +682,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -630,7 +690,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.8122750899640144</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CAAAAGTGTCA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AAAGTGT&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9104358256697321</v>
       </c>
     </row>
@@ -680,7 +760,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAGTGTCATAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -688,7 +768,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AAGTGTCAT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9702119152339065</v>
       </c>
     </row>
@@ -709,7 +799,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAGTGTCATAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -717,7 +807,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGTGTCAT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9726109556177529</v>
       </c>
     </row>
@@ -738,7 +838,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAGTGTCATAA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -746,7 +846,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;GTGTCAT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9872051179528188</v>
       </c>
     </row>
